--- a/artfynd/A 7943-2026 artfynd.xlsx
+++ b/artfynd/A 7943-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420742</v>
+        <v>123420735</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599318</v>
+        <v>599422</v>
       </c>
       <c r="R2" t="n">
-        <v>6828277</v>
+        <v>6828292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2377</t>
+          <t>2024_2383</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420735</v>
+        <v>123420734</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,31 +811,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599422</v>
+        <v>599419</v>
       </c>
       <c r="R3" t="n">
-        <v>6828292</v>
+        <v>6828290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2383</t>
+          <t>2024_2384</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -935,19 +925,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420744</v>
+        <v>123420738</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -984,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599191</v>
+        <v>599381</v>
       </c>
       <c r="R4" t="n">
-        <v>6828240</v>
+        <v>6828287</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2375</t>
+          <t>2024_2380</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,19 +1050,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420738</v>
+        <v>123420744</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599381</v>
+        <v>599191</v>
       </c>
       <c r="R5" t="n">
-        <v>6828287</v>
+        <v>6828240</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2380</t>
+          <t>2024_2375</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,15 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420734</v>
+        <v>123420742</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,26 +1186,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599419</v>
+        <v>599318</v>
       </c>
       <c r="R6" t="n">
-        <v>6828290</v>
+        <v>6828277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2384</t>
+          <t>2024_2377</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
